--- a/Test/TestCase.xlsx
+++ b/Test/TestCase.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\OneDrive\Desktop\online-movie-ticket-booking\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE3C39E-A006-476E-8363-78E6589025BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B2A95F-D62F-4E04-9758-3873F5E2D9FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="88">
   <si>
     <t>Online Movie Ticket Booking System — Test Case Matrix</t>
   </si>
@@ -99,9 +99,6 @@
     <t>Salina Tiwari</t>
   </si>
   <si>
-    <t>2026-03-11</t>
-  </si>
-  <si>
     <t>TC-02</t>
   </si>
   <si>
@@ -120,9 +117,6 @@
     <t>Returned Rs 3,660.00</t>
   </si>
   <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
     <t>TC-03</t>
   </si>
   <si>
@@ -153,9 +147,6 @@
     <t>Second session showed seats as unavailable after 4 seconds</t>
   </si>
   <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
     <t>TC-05</t>
   </si>
   <si>
@@ -174,9 +165,6 @@
     <t>Payment returned SUCCESS; booking record created with status 'Confirmed'</t>
   </si>
   <si>
-    <t>2026-03-16</t>
-  </si>
-  <si>
     <t>TC-06</t>
   </si>
   <si>
@@ -219,9 +207,6 @@
     <t>E-ticket generated and emailed successfully with correct details</t>
   </si>
   <si>
-    <t>2026-03-17</t>
-  </si>
-  <si>
     <t>TC-08</t>
   </si>
   <si>
@@ -255,9 +240,6 @@
     <t>Report displayed Rs 18,300.00 and 5 transactions</t>
   </si>
   <si>
-    <t>2026-03-18</t>
-  </si>
-  <si>
     <t>TC-10</t>
   </si>
   <si>
@@ -274,9 +256,6 @@
   </si>
   <si>
     <t>User completed booking in 4 minutes and rated experience 5/5</t>
-  </si>
-  <si>
-    <t>2026-03-19</t>
   </si>
   <si>
     <t>TC-11</t>
@@ -451,9 +430,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -484,6 +462,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -766,535 +748,535 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
     </row>
     <row r="3" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="14">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="14">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="14">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="6" t="s">
+      <c r="E7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="J7" s="14">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="14">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="14">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="14">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="14">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="14">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="14">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="14">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" s="14">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="3">
+      <c r="B19" s="2">
         <f>COUNTIF($B$4:$B$15,A19)</f>
         <v>3</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <f>COUNTIFS($B$4:$B$15,A19,$H$4:$H$15,"Pass")</f>
         <v>3</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <f>COUNTIFS($B$4:$B$15,A19,$H$4:$H$15,"Fail")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="3">
+      <c r="A20" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="2">
         <f>COUNTIF($B$4:$B$15,A20)</f>
         <v>3</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="2">
         <f>COUNTIFS($B$4:$B$15,A20,$H$4:$H$15,"Pass")</f>
         <v>2</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="2">
         <f>COUNTIFS($B$4:$B$15,A20,$H$4:$H$15,"Fail")</f>
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="3">
+      <c r="A21" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="2">
         <f>COUNTIF($B$4:$B$15,A21)</f>
         <v>3</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="2">
         <f>COUNTIFS($B$4:$B$15,A21,$H$4:$H$15,"Pass")</f>
         <v>3</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="2">
         <f>COUNTIFS($B$4:$B$15,A21,$H$4:$H$15,"Fail")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="3">
+      <c r="A22" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="2">
         <f>COUNTIF($B$4:$B$15,A22)</f>
         <v>3</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="2">
         <f>COUNTIFS($B$4:$B$15,A22,$H$4:$H$15,"Pass")</f>
         <v>2</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="2">
         <f>COUNTIFS($B$4:$B$15,A22,$H$4:$H$15,"Fail")</f>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" s="13">
+      <c r="A23" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" s="12">
         <f>SUM(B19:B22)</f>
         <v>12</v>
       </c>
-      <c r="C23" s="13">
+      <c r="C23" s="12">
         <f>SUM(C19:C22)</f>
         <v>10</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="12">
         <f>SUM(D19:D22)</f>
         <v>2</v>
       </c>
